--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:00:29+00:00</t>
+    <t>2024-02-26T11:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5160,7 +5160,7 @@
         <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5858" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6195" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:04:56+00:00</t>
+    <t>2024-02-26T11:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1162,31 +1162,28 @@
     <t>PID-3</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C</t>
-  </si>
-  <si>
-    <t>INS-C</t>
-  </si>
-  <si>
-    <t>An identifier for this patient</t>
-  </si>
-  <si>
-    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
-  </si>
-  <si>
-    <t>Patient.identifier:INS-C.id</t>
+    <t>Patient.identifier:NSS</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.id</t>
   </si>
   <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.extension</t>
+    <t>Patient.identifier:NSS.extension</t>
   </si>
   <si>
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.use</t>
+    <t>Patient.identifier:NSS.use</t>
   </si>
   <si>
     <t>Patient.identifier.use</t>
@@ -1204,7 +1201,7 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>secondary</t>
+    <t>official</t>
   </si>
   <si>
     <t>Identifies the purpose for this identifier, if known .</t>
@@ -1219,7 +1216,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.type</t>
+    <t>Patient.identifier:NSS.type</t>
   </si>
   <si>
     <t>Patient.identifier.type</t>
@@ -1232,10 +1229,170 @@
     <t>Description of identifier</t>
   </si>
   <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="NH"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.system</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.8</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier.period</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C</t>
+  </si>
+  <si>
+    <t>INS-C</t>
+  </si>
+  <si>
+    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.use</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1247,131 +1404,21 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
     <t>urn:oid:1.2.250.1.213.1.4.2</t>
   </si>
   <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.value</t>
   </si>
   <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.period</t>
   </si>
   <si>
-    <t>Patient.identifier.period</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.assigner</t>
   </si>
   <si>
-    <t>Patient.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
     <t>Patient.identifier:NDP</t>
   </si>
   <si>
@@ -1391,9 +1438,6 @@
   </si>
   <si>
     <t>Patient.identifier:NDP.type</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1405,9 +1449,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
-  </si>
-  <si>
     <t>Patient.identifier:NDP.system</t>
   </si>
   <si>
@@ -1516,7 +1557,7 @@
     <t>INS-NIR</t>
   </si>
   <si>
-    <t>The patient national health identifier INS obtained by requesting the national patient identification service (CNAM) called the INSi teleservice. Identifiant national de santé (NIR) du patient INS provenant du téléservice INSi (service national d'identification des patients (CNAM))</t>
+    <t>INS-NIR - The patient national health identifier INS obtained by requesting the national patient identification service (CNAM) called the INSi teleservice. Identifiant national de santé (NIR) du patient INS provenant du téléservice INSi (service national d'identification des patients (CNAM))</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.id</t>
@@ -1526,9 +1567,6 @@
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.use</t>
-  </si>
-  <si>
-    <t>official</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.type</t>
@@ -1548,9 +1586,6 @@
     <t>Autorité d'affectation des INS-NIR</t>
   </si>
   <si>
-    <t>urn:oid:1.2.250.1.213.1.4.8</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-NIR.value</t>
   </si>
   <si>
@@ -1566,7 +1601,7 @@
     <t>INS-NIA</t>
   </si>
   <si>
-    <t>INS-NIA - The temporary patient's health national identifier obtained by requesting the national patient identification service (CNAM)| Identifiant national temporaire de santé du patient obtenu par interrogation du téléservice INSi de la CNAM</t>
+    <t>INS-NIA - The temporary patient health national identifier obtained by requesting the national patient identification service (CNAM)| Identifiant national temporaire de santé du patient obtenu par interrogation du téléservice INSi de la CNAM</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIA.id</t>
@@ -2872,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO156"/>
+  <dimension ref="A1:AO165"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
@@ -2900,7 +2935,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.0703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>
@@ -7853,7 +7888,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7871,7 +7906,7 @@
         <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -7956,10 +7991,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8071,10 +8106,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8188,10 +8223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8217,16 +8252,16 @@
         <v>173</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -8236,7 +8271,7 @@
         <v>81</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>81</v>
@@ -8254,28 +8289,28 @@
         <v>261</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z46" t="s" s="2">
+      <c r="AA46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8290,7 +8325,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
@@ -8307,10 +8342,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8333,13 +8368,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>391</v>
@@ -8409,7 +8444,7 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -8912,7 +8947,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -9018,7 +9053,7 @@
         <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9133,7 +9168,7 @@
         <v>439</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9250,7 +9285,7 @@
         <v>440</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9276,16 +9311,16 @@
         <v>173</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -9295,7 +9330,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>382</v>
+        <v>441</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -9313,28 +9348,28 @@
         <v>261</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z55" t="s" s="2">
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9349,7 +9384,7 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -9366,10 +9401,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9392,13 +9427,13 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="M56" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>391</v>
@@ -9431,9 +9466,11 @@
       <c r="X56" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y56" s="2"/>
+      <c r="Y56" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>444</v>
+        <v>395</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -9466,7 +9503,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
@@ -9483,7 +9520,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>399</v>
@@ -9494,7 +9531,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -9531,7 +9568,7 @@
         <v>81</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>405</v>
@@ -9602,7 +9639,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>410</v>
@@ -9719,7 +9756,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>419</v>
@@ -9836,7 +9873,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>426</v>
@@ -9953,13 +9990,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>81</v>
@@ -9984,10 +10021,10 @@
         <v>358</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>452</v>
+        <v>360</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -10072,10 +10109,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10187,10 +10224,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10304,10 +10341,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10333,16 +10370,16 @@
         <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10352,7 +10389,7 @@
         <v>81</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>81</v>
@@ -10370,28 +10407,28 @@
         <v>261</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z64" t="s" s="2">
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10406,7 +10443,7 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>81</v>
@@ -10423,10 +10460,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10449,13 +10486,13 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>391</v>
@@ -10471,7 +10508,7 @@
         <v>81</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>81</v>
@@ -10525,7 +10562,7 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10542,7 +10579,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>399</v>
@@ -10590,7 +10627,7 @@
         <v>81</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>405</v>
@@ -10661,7 +10698,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>410</v>
@@ -10778,7 +10815,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>419</v>
@@ -10895,7 +10932,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>426</v>
@@ -11012,13 +11049,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>81</v>
@@ -11028,7 +11065,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -11043,10 +11080,10 @@
         <v>358</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>465</v>
+        <v>360</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -11131,10 +11168,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11246,10 +11283,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11363,10 +11400,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11392,16 +11429,16 @@
         <v>173</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11411,7 +11448,7 @@
         <v>81</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>81</v>
@@ -11429,28 +11466,28 @@
         <v>261</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z73" t="s" s="2">
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11465,7 +11502,7 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
@@ -11485,7 +11522,7 @@
         <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11508,13 +11545,13 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>391</v>
@@ -11584,7 +11621,7 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
@@ -12193,7 +12230,7 @@
         <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12308,7 +12345,7 @@
         <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12425,7 +12462,7 @@
         <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12451,16 +12488,16 @@
         <v>173</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12470,7 +12507,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -12488,28 +12525,28 @@
         <v>261</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12524,7 +12561,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -12541,10 +12578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12567,13 +12604,13 @@
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>391</v>
@@ -12589,7 +12626,7 @@
         <v>81</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>81</v>
@@ -12643,7 +12680,7 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>81</v>
@@ -12660,7 +12697,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>399</v>
@@ -12671,7 +12708,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>89</v>
@@ -12689,7 +12726,7 @@
         <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>401</v>
@@ -12708,7 +12745,7 @@
         <v>81</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>405</v>
@@ -12779,7 +12816,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>410</v>
@@ -12896,7 +12933,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>419</v>
@@ -13013,7 +13050,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>426</v>
@@ -13130,13 +13167,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>81</v>
@@ -13161,7 +13198,7 @@
         <v>358</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>360</v>
@@ -13249,10 +13286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13364,10 +13401,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13481,10 +13518,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13510,16 +13547,16 @@
         <v>173</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13529,7 +13566,7 @@
         <v>81</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>496</v>
+        <v>381</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>81</v>
@@ -13547,28 +13584,28 @@
         <v>261</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13583,7 +13620,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
@@ -13600,10 +13637,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13626,13 +13663,13 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>391</v>
@@ -13648,7 +13685,7 @@
         <v>81</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>81</v>
@@ -13702,7 +13739,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
@@ -13719,7 +13756,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>399</v>
@@ -13748,7 +13785,7 @@
         <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>401</v>
@@ -13767,7 +13804,7 @@
         <v>81</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>501</v>
+        <v>404</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>405</v>
@@ -13838,7 +13875,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>410</v>
@@ -13955,7 +13992,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>419</v>
@@ -14072,7 +14109,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>426</v>
@@ -14189,12 +14226,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>81</v>
       </c>
@@ -14203,38 +14242,34 @@
         <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J97" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>506</v>
+        <v>358</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>510</v>
+        <v>361</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q97" t="s" s="2">
-        <v>511</v>
-      </c>
+      <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
         <v>81</v>
       </c>
@@ -14278,13 +14313,13 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>505</v>
+        <v>357</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>101</v>
@@ -14293,16 +14328,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>512</v>
+        <v>364</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>109</v>
+        <v>365</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>513</v>
+        <v>366</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -14310,10 +14345,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>514</v>
+        <v>372</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14321,10 +14356,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
@@ -14333,23 +14368,19 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>515</v>
+        <v>105</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>516</v>
+        <v>106</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -14385,41 +14416,43 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AC98" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>521</v>
+        <v>109</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14427,16 +14460,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14452,23 +14483,21 @@
         <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>526</v>
+        <v>112</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>527</v>
+        <v>113</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>528</v>
+        <v>114</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14504,19 +14533,19 @@
         <v>81</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>514</v>
+        <v>119</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14528,19 +14557,19 @@
         <v>101</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>81</v>
@@ -14548,10 +14577,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>530</v>
+        <v>376</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14568,22 +14597,26 @@
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>106</v>
+        <v>377</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14592,7 +14625,7 @@
         <v>81</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>81</v>
@@ -14607,13 +14640,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14631,7 +14664,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>108</v>
+        <v>384</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14640,13 +14673,13 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>109</v>
+        <v>385</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>81</v>
@@ -14655,7 +14688,7 @@
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14663,21 +14696,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14686,21 +14719,23 @@
         <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>112</v>
+        <v>388</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>114</v>
+        <v>390</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -14709,7 +14744,7 @@
         <v>81</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>81</v>
@@ -14724,46 +14759,46 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>119</v>
+        <v>396</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>103</v>
+        <v>385</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>81</v>
@@ -14772,7 +14807,7 @@
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14780,10 +14815,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>399</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14791,7 +14826,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -14800,25 +14835,25 @@
         <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>536</v>
+        <v>401</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>537</v>
+        <v>402</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>538</v>
+        <v>403</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14828,10 +14863,10 @@
         <v>81</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>456</v>
+        <v>511</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>81</v>
@@ -14843,13 +14878,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>540</v>
+        <v>81</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14867,7 +14902,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>541</v>
+        <v>406</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14882,7 +14917,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>265</v>
+        <v>407</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>81</v>
@@ -14891,7 +14926,7 @@
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>542</v>
+        <v>408</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14899,10 +14934,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>544</v>
+        <v>410</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14910,7 +14945,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>89</v>
@@ -14928,17 +14963,15 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>545</v>
+        <v>411</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>546</v>
+        <v>412</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14950,7 +14983,7 @@
         <v>81</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>81</v>
@@ -14986,7 +15019,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>548</v>
+        <v>415</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15001,7 +15034,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>285</v>
+        <v>416</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>81</v>
@@ -15010,7 +15043,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>549</v>
+        <v>417</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -15018,14 +15051,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>551</v>
+        <v>419</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15044,16 +15077,16 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>553</v>
+        <v>420</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>554</v>
+        <v>421</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>555</v>
+        <v>345</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15103,7 +15136,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>556</v>
+        <v>422</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15115,10 +15148,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>557</v>
+        <v>423</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>81</v>
@@ -15127,7 +15160,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>558</v>
+        <v>424</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -15135,21 +15168,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>559</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>560</v>
+        <v>426</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -15161,16 +15194,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>105</v>
+        <v>427</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>562</v>
+        <v>428</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>563</v>
+        <v>429</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>564</v>
+        <v>430</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15220,22 +15253,22 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>565</v>
+        <v>431</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>432</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>566</v>
+        <v>433</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>81</v>
@@ -15244,7 +15277,7 @@
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>567</v>
+        <v>434</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>81</v>
@@ -15252,10 +15285,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>568</v>
+        <v>515</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15266,34 +15299,38 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>105</v>
+        <v>516</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>570</v>
+        <v>517</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>571</v>
+        <v>518</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="R106" t="s" s="2">
         <v>81</v>
       </c>
@@ -15337,13 +15374,13 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>572</v>
+        <v>515</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>101</v>
@@ -15352,16 +15389,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>81</v>
+        <v>523</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -15369,10 +15406,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>575</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15380,7 +15417,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>80</v>
@@ -15395,18 +15432,20 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>105</v>
+        <v>525</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>577</v>
+        <v>526</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>578</v>
+        <v>527</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15442,19 +15481,17 @@
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>579</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15469,16 +15506,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>581</v>
+        <v>533</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -15486,12 +15523,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>534</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15500,7 +15539,7 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
@@ -15512,19 +15551,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>342</v>
+        <v>536</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>585</v>
+        <v>538</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>345</v>
+        <v>528</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>586</v>
+        <v>529</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15573,31 +15612,31 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>587</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>349</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>350</v>
+        <v>531</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>588</v>
+        <v>533</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>81</v>
@@ -15605,20 +15644,18 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>589</v>
+        <v>539</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>89</v>
@@ -15630,23 +15667,19 @@
         <v>81</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>526</v>
+        <v>105</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>591</v>
+        <v>106</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15694,31 +15727,31 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>521</v>
+        <v>109</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15726,21 +15759,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>593</v>
+        <v>541</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>81</v>
@@ -15752,15 +15785,17 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15797,34 +15832,34 @@
         <v>81</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>81</v>
@@ -15841,10 +15876,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>594</v>
+        <v>543</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15855,28 +15890,32 @@
         <v>89</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>198</v>
+        <v>545</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15885,7 +15924,7 @@
         <v>81</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>81</v>
@@ -15900,46 +15939,46 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>550</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>119</v>
+        <v>551</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>81</v>
@@ -15948,7 +15987,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15956,20 +15995,18 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>595</v>
+        <v>553</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>89</v>
@@ -15981,19 +16018,23 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>597</v>
+        <v>105</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>598</v>
+        <v>555</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
@@ -16041,22 +16082,22 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>119</v>
+        <v>558</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>81</v>
@@ -16065,7 +16106,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -16073,18 +16114,18 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>89</v>
@@ -16093,26 +16134,24 @@
         <v>81</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>81</v>
       </c>
@@ -16121,7 +16160,7 @@
         <v>81</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>81</v>
@@ -16136,13 +16175,13 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>540</v>
+        <v>81</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -16160,7 +16199,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16175,7 +16214,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>265</v>
+        <v>567</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>81</v>
@@ -16184,7 +16223,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -16192,21 +16231,21 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>81</v>
+        <v>571</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>81</v>
@@ -16221,17 +16260,15 @@
         <v>105</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>546</v>
+        <v>573</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>81</v>
       </c>
@@ -16279,13 +16316,13 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>101</v>
@@ -16294,7 +16331,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>285</v>
+        <v>576</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>81</v>
@@ -16303,7 +16340,7 @@
         <v>81</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -16311,21 +16348,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
@@ -16340,13 +16377,13 @@
         <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>554</v>
+        <v>581</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>555</v>
+        <v>291</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16396,13 +16433,13 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>101</v>
@@ -16411,7 +16448,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>81</v>
@@ -16420,7 +16457,7 @@
         <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16428,21 +16465,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>81</v>
@@ -16457,13 +16494,13 @@
         <v>105</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>564</v>
+        <v>291</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16513,7 +16550,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16528,7 +16565,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>81</v>
@@ -16537,7 +16574,7 @@
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16545,10 +16582,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16559,7 +16596,7 @@
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
@@ -16571,18 +16608,20 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16630,22 +16669,22 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>573</v>
+        <v>350</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>81</v>
@@ -16654,7 +16693,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16662,21 +16701,23 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>81</v>
@@ -16688,18 +16729,20 @@
         <v>90</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>105</v>
+        <v>536</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16747,7 +16790,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>579</v>
+        <v>524</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16762,16 +16805,16 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>581</v>
+        <v>533</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16779,10 +16822,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>583</v>
+        <v>540</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16802,23 +16845,19 @@
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>584</v>
+        <v>106</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>81</v>
       </c>
@@ -16866,7 +16905,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16875,13 +16914,13 @@
         <v>89</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>350</v>
+        <v>109</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>81</v>
@@ -16890,7 +16929,7 @@
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>588</v>
+        <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16898,10 +16937,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>608</v>
+        <v>542</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16909,7 +16948,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>80</v>
@@ -16924,20 +16963,16 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>609</v>
+        <v>112</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>610</v>
+        <v>198</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>81</v>
       </c>
@@ -16973,19 +17008,19 @@
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>608</v>
+        <v>119</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16997,10 +17032,10 @@
         <v>101</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>614</v>
+        <v>120</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>81</v>
@@ -17009,7 +17044,7 @@
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>616</v>
+        <v>81</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>81</v>
@@ -17017,12 +17052,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
       </c>
@@ -17040,23 +17077,19 @@
         <v>81</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>173</v>
+        <v>607</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
@@ -17080,11 +17113,13 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>622</v>
+        <v>81</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -17102,31 +17137,31 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>617</v>
+        <v>119</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>623</v>
+        <v>81</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>624</v>
+        <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>625</v>
+        <v>81</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>81</v>
@@ -17134,10 +17169,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>544</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17154,25 +17189,25 @@
         <v>81</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>627</v>
+        <v>173</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>628</v>
+        <v>545</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>629</v>
+        <v>546</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>630</v>
+        <v>547</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -17182,7 +17217,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -17197,13 +17232,13 @@
         <v>81</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>81</v>
+        <v>550</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>81</v>
@@ -17221,7 +17256,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>626</v>
+        <v>551</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17236,27 +17271,27 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>632</v>
+        <v>265</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>633</v>
+        <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>634</v>
+        <v>552</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>635</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>636</v>
+        <v>554</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17273,25 +17308,25 @@
         <v>81</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>637</v>
+        <v>105</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>638</v>
+        <v>555</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>639</v>
+        <v>556</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>640</v>
+        <v>557</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>641</v>
+        <v>282</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -17340,7 +17375,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>636</v>
+        <v>558</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17355,16 +17390,16 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>642</v>
+        <v>285</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>643</v>
+        <v>559</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -17372,21 +17407,21 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>644</v>
+        <v>561</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
@@ -17395,23 +17430,21 @@
         <v>81</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>239</v>
+        <v>563</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>240</v>
+        <v>564</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>645</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>81</v>
       </c>
@@ -17459,13 +17492,13 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>644</v>
+        <v>566</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>101</v>
@@ -17474,7 +17507,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>243</v>
+        <v>567</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>81</v>
@@ -17483,7 +17516,7 @@
         <v>81</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>244</v>
+        <v>568</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17491,18 +17524,18 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>646</v>
+        <v>613</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>646</v>
+        <v>570</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>81</v>
+        <v>571</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>89</v>
@@ -17514,23 +17547,21 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>389</v>
+        <v>105</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>648</v>
+        <v>573</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>650</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17554,11 +17585,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17576,13 +17609,13 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>646</v>
+        <v>575</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>101</v>
@@ -17591,16 +17624,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>652</v>
+        <v>576</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>653</v>
+        <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>654</v>
+        <v>577</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17608,10 +17641,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>655</v>
+        <v>579</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17622,7 +17655,7 @@
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17631,23 +17664,21 @@
         <v>81</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>656</v>
+        <v>105</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>657</v>
+        <v>580</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17695,13 +17726,13 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>655</v>
+        <v>582</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>101</v>
@@ -17710,16 +17741,16 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>661</v>
+        <v>583</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>662</v>
+        <v>584</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17727,10 +17758,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>663</v>
+        <v>616</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>663</v>
+        <v>586</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17750,23 +17781,21 @@
         <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>664</v>
+        <v>105</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>665</v>
+        <v>587</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>666</v>
+        <v>588</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17814,7 +17843,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>663</v>
+        <v>589</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17826,19 +17855,19 @@
         <v>101</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>669</v>
+        <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>670</v>
+        <v>590</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17846,10 +17875,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>672</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>672</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17860,7 +17889,7 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
@@ -17869,22 +17898,22 @@
         <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>673</v>
+        <v>342</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>674</v>
+        <v>594</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>675</v>
+        <v>595</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>676</v>
+        <v>345</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>677</v>
+        <v>596</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17933,31 +17962,31 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>672</v>
+        <v>597</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>678</v>
+        <v>349</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>679</v>
+        <v>350</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>81</v>
+        <v>598</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -17965,10 +17994,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17979,7 +18008,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>81</v>
@@ -17991,16 +18020,20 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>619</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>106</v>
+        <v>620</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
@@ -18048,22 +18081,22 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>108</v>
+        <v>618</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>624</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>109</v>
+        <v>625</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>81</v>
@@ -18072,7 +18105,7 @@
         <v>81</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>81</v>
+        <v>626</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>81</v>
@@ -18080,21 +18113,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>681</v>
+        <v>627</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>681</v>
+        <v>627</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -18103,21 +18136,23 @@
         <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>628</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
+        <v>629</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -18141,55 +18176,53 @@
         <v>81</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>81</v>
+        <v>632</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>627</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>103</v>
+        <v>633</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>81</v>
+        <v>634</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>81</v>
+        <v>635</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>81</v>
@@ -18197,20 +18230,18 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>682</v>
+        <v>636</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>89</v>
@@ -18222,19 +18253,23 @@
         <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>684</v>
+        <v>637</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>685</v>
+        <v>638</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
       </c>
@@ -18282,46 +18317,44 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>119</v>
+        <v>636</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>81</v>
+        <v>642</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>81</v>
+        <v>643</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>81</v>
+        <v>644</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>81</v>
+        <v>645</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>688</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18336,22 +18369,26 @@
         <v>81</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>689</v>
+        <v>647</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>690</v>
+        <v>648</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18399,31 +18436,31 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>119</v>
+        <v>646</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>81</v>
+        <v>652</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>81</v>
+        <v>653</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18431,14 +18468,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>692</v>
+        <v>654</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>692</v>
+        <v>654</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>693</v>
+        <v>81</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18451,25 +18488,25 @@
         <v>81</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>694</v>
+        <v>239</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>695</v>
+        <v>240</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>355</v>
+        <v>655</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18518,7 +18555,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>696</v>
+        <v>654</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18530,10 +18567,10 @@
         <v>101</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>81</v>
@@ -18542,7 +18579,7 @@
         <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>81</v>
@@ -18550,10 +18587,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>697</v>
+        <v>656</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>697</v>
+        <v>656</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18561,7 +18598,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>89</v>
@@ -18576,19 +18613,19 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>698</v>
+        <v>657</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>699</v>
+        <v>658</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18615,33 +18652,33 @@
       <c r="X134" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y134" t="s" s="2">
-        <v>701</v>
-      </c>
+      <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>702</v>
+        <v>661</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="AC134" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>697</v>
+        <v>656</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>101</v>
@@ -18650,16 +18687,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>704</v>
+        <v>662</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>109</v>
+        <v>663</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>705</v>
+        <v>664</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>81</v>
@@ -18667,14 +18704,12 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>706</v>
+        <v>665</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>707</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18695,19 +18730,19 @@
         <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>389</v>
+        <v>666</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>699</v>
+        <v>668</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18732,11 +18767,13 @@
         <v>81</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y135" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z135" t="s" s="2">
-        <v>709</v>
+        <v>81</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>81</v>
@@ -18754,13 +18791,13 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>697</v>
+        <v>665</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>101</v>
@@ -18769,7 +18806,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>704</v>
+        <v>671</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>109</v>
@@ -18778,7 +18815,7 @@
         <v>81</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>705</v>
+        <v>672</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>81</v>
@@ -18786,14 +18823,12 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>710</v>
+        <v>673</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>711</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>81</v>
       </c>
@@ -18802,7 +18837,7 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>81</v>
@@ -18814,19 +18849,19 @@
         <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>389</v>
+        <v>674</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>712</v>
+        <v>675</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>699</v>
+        <v>676</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>700</v>
+        <v>678</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18851,11 +18886,13 @@
         <v>81</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z136" t="s" s="2">
-        <v>713</v>
+        <v>81</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>81</v>
@@ -18873,7 +18910,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>697</v>
+        <v>673</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18885,10 +18922,10 @@
         <v>101</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>679</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>704</v>
+        <v>680</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>109</v>
@@ -18897,7 +18934,7 @@
         <v>81</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>705</v>
+        <v>681</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>81</v>
@@ -18905,10 +18942,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>714</v>
+        <v>682</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>714</v>
+        <v>682</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18919,7 +18956,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>81</v>
@@ -18931,19 +18968,19 @@
         <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>515</v>
+        <v>683</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>716</v>
+        <v>685</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -18992,31 +19029,31 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>714</v>
+        <v>682</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>102</v>
+        <v>688</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>719</v>
+        <v>689</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>720</v>
+        <v>81</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>81</v>
@@ -19024,10 +19061,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19038,7 +19075,7 @@
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>81</v>
@@ -19050,20 +19087,16 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>609</v>
+        <v>105</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>610</v>
+        <v>106</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
       </c>
@@ -19111,22 +19144,22 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>721</v>
+        <v>108</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>614</v>
+        <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>615</v>
+        <v>109</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>81</v>
@@ -19135,7 +19168,7 @@
         <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>616</v>
+        <v>81</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19143,21 +19176,21 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>723</v>
+        <v>691</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>723</v>
+        <v>691</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
@@ -19169,20 +19202,18 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>724</v>
+        <v>112</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>725</v>
+        <v>113</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>726</v>
+        <v>114</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>727</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>81</v>
       </c>
@@ -19218,43 +19249,43 @@
         <v>81</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>723</v>
+        <v>119</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>728</v>
+        <v>103</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>81</v>
@@ -19262,12 +19293,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>730</v>
+        <v>692</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>693</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19288,20 +19321,16 @@
         <v>81</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>173</v>
+        <v>694</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>731</v>
+        <v>695</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19325,13 +19354,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>734</v>
+        <v>81</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>735</v>
+        <v>81</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19349,31 +19378,31 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>730</v>
+        <v>119</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>623</v>
+        <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>736</v>
+        <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -19381,12 +19410,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>737</v>
+        <v>697</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="C141" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="D141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19407,20 +19438,16 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>427</v>
+        <v>699</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>738</v>
+        <v>700</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>741</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19468,31 +19495,31 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>737</v>
+        <v>119</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>742</v>
+        <v>101</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>432</v>
+        <v>120</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>743</v>
+        <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>744</v>
+        <v>81</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -19500,44 +19527,46 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>745</v>
+        <v>702</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>745</v>
+        <v>702</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>81</v>
+        <v>703</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>342</v>
+        <v>112</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>746</v>
+        <v>704</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>747</v>
+        <v>705</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19585,31 +19614,31 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>349</v>
+        <v>120</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>748</v>
+        <v>103</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>749</v>
+        <v>81</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>81</v>
@@ -19617,10 +19646,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>750</v>
+        <v>707</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>750</v>
+        <v>707</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19628,10 +19657,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19643,19 +19672,19 @@
         <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>673</v>
+        <v>388</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>751</v>
+        <v>708</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>752</v>
+        <v>709</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>753</v>
+        <v>659</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>754</v>
+        <v>710</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19680,31 +19709,29 @@
         <v>81</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>81</v>
+        <v>711</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>81</v>
+        <v>712</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>750</v>
+        <v>707</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19719,16 +19746,16 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>755</v>
+        <v>714</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>756</v>
+        <v>109</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>81</v>
+        <v>715</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>81</v>
@@ -19736,12 +19763,14 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>757</v>
+        <v>716</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="C144" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
       </c>
@@ -19762,16 +19791,20 @@
         <v>81</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>105</v>
+        <v>388</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>106</v>
+        <v>718</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>710</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>81</v>
       </c>
@@ -19795,13 +19828,11 @@
         <v>81</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>81</v>
+        <v>719</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>81</v>
@@ -19819,31 +19850,31 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>108</v>
+        <v>707</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AL144" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AL144" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>81</v>
+        <v>715</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -19851,21 +19882,23 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>758</v>
+        <v>720</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>721</v>
+      </c>
       <c r="D145" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>81</v>
@@ -19877,18 +19910,20 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>112</v>
+        <v>388</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>113</v>
+        <v>722</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>114</v>
+        <v>709</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>710</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>81</v>
       </c>
@@ -19912,31 +19947,29 @@
         <v>81</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>81</v>
+        <v>723</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>119</v>
+        <v>707</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19948,19 +19981,19 @@
         <v>101</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>103</v>
+        <v>714</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>81</v>
+        <v>715</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>81</v>
@@ -19968,45 +20001,45 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>759</v>
+        <v>724</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>759</v>
+        <v>724</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>693</v>
+        <v>81</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>112</v>
+        <v>525</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>694</v>
+        <v>725</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>115</v>
+        <v>727</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>355</v>
+        <v>728</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>81</v>
@@ -20055,22 +20088,22 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>103</v>
+        <v>729</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>81</v>
@@ -20079,7 +20112,7 @@
         <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>81</v>
+        <v>730</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>81</v>
@@ -20087,10 +20120,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>760</v>
+        <v>731</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>760</v>
+        <v>731</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20098,10 +20131,10 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>81</v>
@@ -20113,19 +20146,19 @@
         <v>81</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>389</v>
+        <v>619</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>761</v>
+        <v>620</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>762</v>
+        <v>621</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>764</v>
+        <v>623</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
@@ -20150,13 +20183,13 @@
         <v>81</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>81</v>
@@ -20174,31 +20207,31 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>760</v>
+        <v>731</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>624</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>765</v>
+        <v>625</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>766</v>
+        <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>767</v>
+        <v>626</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -20206,10 +20239,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20232,19 +20265,19 @@
         <v>81</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>506</v>
+        <v>734</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>769</v>
+        <v>735</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>770</v>
+        <v>736</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>771</v>
+        <v>241</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>772</v>
+        <v>737</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20293,7 +20326,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20308,16 +20341,16 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>773</v>
+        <v>738</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>774</v>
+        <v>109</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -20325,21 +20358,21 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>777</v>
+        <v>81</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>81</v>
@@ -20351,18 +20384,20 @@
         <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>778</v>
+        <v>173</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>779</v>
+        <v>741</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>780</v>
+        <v>742</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="O149" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>743</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
       </c>
@@ -20386,13 +20421,13 @@
         <v>81</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>81</v>
+        <v>744</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>81</v>
+        <v>745</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20410,22 +20445,22 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>432</v>
+        <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>782</v>
+        <v>633</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>109</v>
@@ -20434,7 +20469,7 @@
         <v>81</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>783</v>
+        <v>746</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>81</v>
@@ -20442,10 +20477,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>784</v>
+        <v>747</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>784</v>
+        <v>747</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20465,22 +20500,22 @@
         <v>81</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>785</v>
+        <v>427</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>786</v>
+        <v>748</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>787</v>
+        <v>749</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>788</v>
+        <v>750</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>789</v>
+        <v>751</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20529,7 +20564,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>784</v>
+        <v>747</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20538,22 +20573,22 @@
         <v>89</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>101</v>
+        <v>752</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>432</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>790</v>
+        <v>109</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>81</v>
+        <v>754</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -20561,10 +20596,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20575,32 +20610,30 @@
         <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>673</v>
+        <v>342</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>792</v>
+        <v>756</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>793</v>
+        <v>757</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>795</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>81</v>
       </c>
@@ -20648,22 +20681,22 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>796</v>
+        <v>758</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>109</v>
@@ -20672,7 +20705,7 @@
         <v>81</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>81</v>
+        <v>759</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>81</v>
@@ -20680,10 +20713,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20694,7 +20727,7 @@
         <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>81</v>
@@ -20706,16 +20739,20 @@
         <v>81</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>105</v>
+        <v>683</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>106</v>
+        <v>761</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>762</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>764</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20763,25 +20800,25 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>108</v>
+        <v>760</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>109</v>
+        <v>765</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>81</v>
+        <v>766</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>81</v>
@@ -20795,21 +20832,21 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>81</v>
@@ -20821,17 +20858,15 @@
         <v>81</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -20868,34 +20903,34 @@
         <v>81</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>81</v>
@@ -20912,14 +20947,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>693</v>
+        <v>111</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20932,26 +20967,24 @@
         <v>81</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K154" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>694</v>
+        <v>113</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>695</v>
+        <v>114</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O154" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -20987,19 +21020,19 @@
         <v>81</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>696</v>
+        <v>119</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21031,44 +21064,46 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>81</v>
+        <v>703</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J155" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>801</v>
+        <v>112</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>802</v>
+        <v>704</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>803</v>
+        <v>705</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -21116,31 +21151,31 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>800</v>
+        <v>706</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>432</v>
+        <v>120</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>805</v>
+        <v>81</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
@@ -21148,10 +21183,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>806</v>
+        <v>770</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>806</v>
+        <v>770</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21171,21 +21206,23 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>173</v>
+        <v>388</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>807</v>
+        <v>771</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>808</v>
+        <v>772</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O156" s="2"/>
+        <v>773</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
       </c>
@@ -21209,13 +21246,13 @@
         <v>81</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>261</v>
+        <v>177</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>808</v>
+        <v>178</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>809</v>
+        <v>179</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
@@ -21233,7 +21270,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>806</v>
+        <v>770</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>89</v>
@@ -21248,18 +21285,1077 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="P157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="P159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="P160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO162" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="P163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO163" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AL156" t="s" s="2">
+      <c r="B164" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="O164" s="2"/>
+      <c r="P164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL164" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AM156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO156" t="s" s="2">
+      <c r="AM164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AO164" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO165" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:06:19+00:00</t>
+    <t>2024-02-27T11:09:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:09:52+00:00</t>
+    <t>2024-02-27T11:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-update-patient-ins/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T11:11:58+00:00</t>
+    <t>2024-02-27T13:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,7 +273,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}fr-core-1:If identityReliability status = VALI, then Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or both SHALL be present {extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').valueCoding.code = VALI implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists())}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}fr-core-1:If identityReliability status = 'VALI', then Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or both SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
